--- a/student_registration_forms/020_exam_grade_entry_form--student_registration_forms.xlsx
+++ b/student_registration_forms/020_exam_grade_entry_form--student_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'assignment_1',_'value':_'assignment_1'}</t>
+          <t>assignment_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Assignment 1', 'value': 'Assignment 1'}</t>
+          <t>Assignment 1</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'assignment_2',_'value':_'assignment_2'}</t>
+          <t>assignment_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Assignment 2', 'value': 'Assignment 2'}</t>
+          <t>Assignment 2</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'other',_'value':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Other', 'value': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'not_applicable',_'value':_'not_applicable'}</t>
+          <t>not_applicable</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Not Applicable', 'value': 'Not Applicable'}</t>
+          <t>Not Applicable</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'letter_grade',_'value':_'letter'}</t>
+          <t>letter_grade</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Letter Grade', 'value': 'letter'}</t>
+          <t>Letter Grade</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'percent',_'value':_'percent'}</t>
+          <t>percent</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Percent', 'value': 'percent'}</t>
+          <t>Percent</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'fall_2022',_'value':_'fall_2022'}</t>
+          <t>fall_2022</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Fall 2022', 'value': 'Fall 2022'}</t>
+          <t>Fall 2022</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'spring_2023',_'value':_'spring_2023'}</t>
+          <t>spring_2023</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Spring 2023', 'value': 'Spring 2023'}</t>
+          <t>Spring 2023</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'a+',_'value':_'a+'}</t>
+          <t>a+</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'A+', 'value': 'A+'}</t>
+          <t>A+</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'a',_'value':_'a'}</t>
+          <t>a</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'A', 'value': 'A'}</t>
+          <t>A</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'b',_'value':_'b'}</t>
+          <t>b</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'B', 'value': 'B'}</t>
+          <t>B</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'c',_'value':_'c'}</t>
+          <t>c</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'C', 'value': 'C'}</t>
+          <t>C</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'d',_'value':_'d'}</t>
+          <t>d</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'D', 'value': 'D'}</t>
+          <t>D</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'f',_'value':_'f'}</t>
+          <t>f</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'F', 'value': 'F'}</t>
+          <t>F</t>
         </is>
       </c>
     </row>
